--- a/data/trans_orig/P05A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>208433</t>
+          <t>205690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>257791</t>
+          <t>258355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>232029</t>
+          <t>232954</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>281848</t>
+          <t>281499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>457580</t>
+          <t>457205</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>526417</t>
+          <t>526186</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>436221</t>
+          <t>435657</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>485579</t>
+          <t>488322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>406503</t>
+          <t>406852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>456322</t>
+          <t>455397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>855946</t>
+          <t>856177</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>924783</t>
+          <t>925158</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>256551</t>
+          <t>258519</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>317405</t>
+          <t>315695</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>322501</t>
+          <t>320867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>386425</t>
+          <t>381907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>597673</t>
+          <t>595749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>682574</t>
+          <t>680231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>644395</t>
+          <t>646105</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>705249</t>
+          <t>703281</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>581968</t>
+          <t>586486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>645892</t>
+          <t>647526</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1247619</t>
+          <t>1249962</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1332520</t>
+          <t>1334444</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167514</t>
+          <t>168835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215947</t>
+          <t>216480</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,47 +1434,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>24,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>188988</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>168865</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>212721</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>27,64%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>24,69%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>188988</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>166516</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>212663</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>346731</t>
+          <t>347497</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>413487</t>
+          <t>414634</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>462562</t>
+          <t>462029</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>510995</t>
+          <t>509674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,49 +1547,49 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>75,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>494853</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>471120</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>514976</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>72,36%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>68,89%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>75,31%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>501</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>494853</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>471178</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>517325</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>68,9%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>75,65%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>964</t>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>948863</t>
+          <t>947716</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1015619</t>
+          <t>1014853</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,49%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230773</t>
+          <t>231714</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>285929</t>
+          <t>288837</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>333190</t>
+          <t>331547</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>393295</t>
+          <t>393666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>584305</t>
+          <t>585286</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>666687</t>
+          <t>663785</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>656293</t>
+          <t>653385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>711449</t>
+          <t>710508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>645317</t>
+          <t>644946</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>705422</t>
+          <t>707065</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1314147</t>
+          <t>1317049</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1396529</t>
+          <t>1395548</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>919208</t>
+          <t>920308</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1028197</t>
+          <t>1021510</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1107855</t>
+          <t>1111094</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1219558</t>
+          <t>1220849</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2057115</t>
+          <t>2048095</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2216172</t>
+          <t>2207510</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2248346</t>
+          <t>2255033</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2357335</t>
+          <t>2356235</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2159639</t>
+          <t>2158348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2271342</t>
+          <t>2268103</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4439569</t>
+          <t>4448231</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4598626</t>
+          <t>4607646</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,23%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>247320</t>
+          <t>247538</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>301788</t>
+          <t>298491</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>238417</t>
+          <t>238098</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>293005</t>
+          <t>289836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>499736</t>
+          <t>500110</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>574303</t>
+          <t>572647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399411</t>
+          <t>402708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453879</t>
+          <t>453661</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>402326</t>
+          <t>405495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>456914</t>
+          <t>457233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>822227</t>
+          <t>823883</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>896794</t>
+          <t>896420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>291326</t>
+          <t>290803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>351344</t>
+          <t>352815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>298851</t>
+          <t>300073</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>363736</t>
+          <t>364520</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>608129</t>
+          <t>607979</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>698350</t>
+          <t>694431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>663459</t>
+          <t>661988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>723477</t>
+          <t>724000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>666333</t>
+          <t>665549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>731218</t>
+          <t>729996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1346522</t>
+          <t>1350441</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1436743</t>
+          <t>1436893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,27%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>262441</t>
+          <t>265430</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>320616</t>
+          <t>321399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>283354</t>
+          <t>282849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>341227</t>
+          <t>340028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>563103</t>
+          <t>562939</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>642492</t>
+          <t>642838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>41,91%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>437007</t>
+          <t>436224</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>495182</t>
+          <t>492193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>434886</t>
+          <t>436085</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>492759</t>
+          <t>493264</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>891245</t>
+          <t>890899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>970634</t>
+          <t>970798</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,3%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>440721</t>
+          <t>442730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>503305</t>
+          <t>506717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>476396</t>
+          <t>476064</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>541374</t>
+          <t>542329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>932867</t>
+          <t>937449</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1026486</t>
+          <t>1025773</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>444434</t>
+          <t>441022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>507018</t>
+          <t>505009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>509571</t>
+          <t>508616</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>574549</t>
+          <t>574881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>972198</t>
+          <t>972911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1065817</t>
+          <t>1061235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1300708</t>
+          <t>1298317</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1414412</t>
+          <t>1417843</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1359477</t>
+          <t>1359339</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1478927</t>
+          <t>1479418</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2690560</t>
+          <t>2683574</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2866196</t>
+          <t>2858180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2006953</t>
+          <t>2003522</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2120657</t>
+          <t>2123048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2073531</t>
+          <t>2073040</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2192981</t>
+          <t>2193119</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,73%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4107627</t>
+          <t>4115643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4283263</t>
+          <t>4290249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>230611</t>
+          <t>233119</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>280799</t>
+          <t>281701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>236777</t>
+          <t>234353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>284652</t>
+          <t>284016</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>479815</t>
+          <t>478832</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>553092</t>
+          <t>551190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>394001</t>
+          <t>393099</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>444189</t>
+          <t>441681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>388187</t>
+          <t>388823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>436062</t>
+          <t>438486</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>794547</t>
+          <t>796449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>867824</t>
+          <t>868807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>283633</t>
+          <t>280734</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>342413</t>
+          <t>345086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>286317</t>
+          <t>286428</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>347605</t>
+          <t>344978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>585546</t>
+          <t>585332</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>673551</t>
+          <t>675367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680018</t>
+          <t>677345</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>738798</t>
+          <t>741697</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>695308</t>
+          <t>697935</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>756596</t>
+          <t>756485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1391793</t>
+          <t>1389977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1479798</t>
+          <t>1480012</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>269775</t>
+          <t>268704</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>325019</t>
+          <t>323200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>282998</t>
+          <t>280418</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>338939</t>
+          <t>338301</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>571370</t>
+          <t>568319</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>646622</t>
+          <t>649271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,07%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>434533</t>
+          <t>436352</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>489777</t>
+          <t>490848</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>444801</t>
+          <t>445439</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>500742</t>
+          <t>503322</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>896670</t>
+          <t>894021</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>971922</t>
+          <t>974973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>326023</t>
+          <t>326523</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>387205</t>
+          <t>384030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>381963</t>
+          <t>378310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>444748</t>
+          <t>445140</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>722597</t>
+          <t>720679</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>808714</t>
+          <t>809856</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>549095</t>
+          <t>552270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>610277</t>
+          <t>609777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597996</t>
+          <t>597604</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>660781</t>
+          <t>664434</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,35%</t>
+          <t>57,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1170330</t>
+          <t>1169188</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1256447</t>
+          <t>1258365</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1165437</t>
+          <t>1164617</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1276521</t>
+          <t>1275558</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1235034</t>
+          <t>1236745</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1354433</t>
+          <t>1356620</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2438907</t>
+          <t>2437893</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2595963</t>
+          <t>2595935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2116562</t>
+          <t>2117525</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2227646</t>
+          <t>2228466</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2187803</t>
+          <t>2185616</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2307202</t>
+          <t>2305491</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4339356</t>
+          <t>4339384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4496412</t>
+          <t>4497426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,85%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46075</t>
+          <t>48946</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>36026</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62514</t>
+          <t>65902</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43574</t>
+          <t>47321</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32633</t>
+          <t>37896</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57480</t>
+          <t>60734</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>89648</t>
+          <t>96267</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72139</t>
+          <t>77827</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108871</t>
+          <t>115906</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>589366</t>
+          <t>641764</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>572927</t>
+          <t>624808</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>602179</t>
+          <t>654684</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>681756</t>
+          <t>686859</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>667850</t>
+          <t>673446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>692697</t>
+          <t>696284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1271124</t>
+          <t>1328622</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1251901</t>
+          <t>1308983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1288633</t>
+          <t>1347062</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>116441</t>
+          <t>122556</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55075</t>
+          <t>100678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>162941</t>
+          <t>147978</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>136587</t>
+          <t>151956</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118218</t>
+          <t>131894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>157531</t>
+          <t>173697</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>253028</t>
+          <t>274512</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167346</t>
+          <t>242492</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>299142</t>
+          <t>305634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1076423</t>
+          <t>926361</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1029923</t>
+          <t>900939</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1137789</t>
+          <t>948239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>821452</t>
+          <t>918833</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>800508</t>
+          <t>897092</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>839821</t>
+          <t>938895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1897875</t>
+          <t>1845194</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1851761</t>
+          <t>1814072</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1983557</t>
+          <t>1877214</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958039</t>
+          <t>1070789</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958039</t>
+          <t>1070789</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958039</t>
+          <t>1070789</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150903</t>
+          <t>2119706</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150903</t>
+          <t>2119706</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150903</t>
+          <t>2119706</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>129838</t>
+          <t>151732</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107683</t>
+          <t>128349</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158880</t>
+          <t>180121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>340663</t>
+          <t>157028</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>162414</t>
+          <t>138166</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>629477</t>
+          <t>180410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>470501</t>
+          <t>308760</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>292053</t>
+          <t>276148</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>864883</t>
+          <t>343175</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>574678</t>
+          <t>650163</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>545636</t>
+          <t>621774</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>596833</t>
+          <t>673546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>592703</t>
+          <t>655231</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>303889</t>
+          <t>631849</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770952</t>
+          <t>674093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1167380</t>
+          <t>1305394</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>772998</t>
+          <t>1270979</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1345828</t>
+          <t>1338006</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>78,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>302245</t>
+          <t>331759</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>273562</t>
+          <t>301155</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>336285</t>
+          <t>361862</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>354262</t>
+          <t>405002</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>287367</t>
+          <t>376733</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>389825</t>
+          <t>434461</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>656508</t>
+          <t>736761</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>580157</t>
+          <t>695491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>701612</t>
+          <t>780378</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>624422</t>
+          <t>657185</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>590382</t>
+          <t>627082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>653105</t>
+          <t>687789</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>739940</t>
+          <t>713293</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>704377</t>
+          <t>683834</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>806835</t>
+          <t>741562</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1364362</t>
+          <t>1370479</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1319258</t>
+          <t>1326862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1440713</t>
+          <t>1411749</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094202</t>
+          <t>1118295</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2020870</t>
+          <t>2107240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2020870</t>
+          <t>2107240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2020870</t>
+          <t>2107240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>594599</t>
+          <t>654993</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>466842</t>
+          <t>602590</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>661663</t>
+          <t>704913</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>875086</t>
+          <t>761307</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>695495</t>
+          <t>722211</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1443886</t>
+          <t>810247</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1469685</t>
+          <t>1416300</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1260212</t>
+          <t>1351245</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2067857</t>
+          <t>1485075</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2864890</t>
+          <t>2875473</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2797826</t>
+          <t>2825553</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2992647</t>
+          <t>2927876</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2835852</t>
+          <t>2974216</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2267052</t>
+          <t>2925276</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3015443</t>
+          <t>3013312</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>5700741</t>
+          <t>5849689</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5102569</t>
+          <t>5780914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5910214</t>
+          <t>5914744</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459489</t>
+          <t>3530466</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459489</t>
+          <t>3530466</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459489</t>
+          <t>3530466</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3710938</t>
+          <t>3735523</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3710938</t>
+          <t>3735523</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3710938</t>
+          <t>3735523</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7170426</t>
+          <t>7265989</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7170426</t>
+          <t>7265989</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7170426</t>
+          <t>7265989</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
